--- a/data/trans_orig/IQ09_A-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IQ09_A-Habitat-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Tiempo medio en años que llevan sufriendo esa dolencia, enfermedad o impedimento que les haya limitado de forma continuada (más de 10 días en los últimos 12 meses)</t>
+          <t>Tiempo medio en años que llevan sufriendo esa dolencia, enfermedad o impedimento que les haya limitado de forma continuada (más de 10 días en los últimos 12 meses) (tasa de respuesta: 97,84%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -721,7 +721,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,97; 4,31</t>
+          <t>1,2; 4,43</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -731,47 +731,47 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,85; 10,71</t>
+          <t>1,74; 10,24</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,34; 5,17</t>
+          <t>0,18; 5,17</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,43; 7,67</t>
+          <t>1,24; 7,79</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,41; 4,72</t>
+          <t>0,76; 4,75</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,16; 6,65</t>
+          <t>1,23; 6,85</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,86; 3,89</t>
+          <t>0,77; 3,73</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,89; 5,56</t>
+          <t>1,97; 5,81</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,83; 3,35</t>
+          <t>0,94; 3,83</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,38; 7,68</t>
+          <t>2,15; 7,25</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,99; 3,43</t>
+          <t>0,9; 3,29</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,99; 4,22</t>
+          <t>1,06; 4,15</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,84; 5,88</t>
+          <t>0,85; 5,84</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,42; 2,85</t>
+          <t>0,36; 2,81</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,27; 7,87</t>
+          <t>2,13; 8,23</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,19; 4,76</t>
+          <t>1,26; 4,7</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,99; 7,54</t>
+          <t>1,98; 7,83</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,52; 6,79</t>
+          <t>2,47; 6,82</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,18; 6,26</t>
+          <t>2,28; 6,53</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,31; 3,6</t>
+          <t>1,45; 3,62</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,69; 5,44</t>
+          <t>1,83; 5,52</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,07; 4,86</t>
+          <t>2,08; 4,83</t>
         </is>
       </c>
     </row>
@@ -996,22 +996,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,46</t>
+          <t>0,0; 10,8</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,55; 6,03</t>
+          <t>0,63; 5,61</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,59</t>
+          <t>0,0; 1,6</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,39; 7,09</t>
+          <t>0,42; 7,3</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1021,37 +1021,37 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,94</t>
+          <t>0,0; 0,89</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,16; 3,91</t>
+          <t>0,16; 3,44</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,02; 11,91</t>
+          <t>1,02; 12,15</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,05; 8,16</t>
+          <t>1,03; 8,11</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,4; 3,09</t>
+          <t>0,41; 2,94</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,24; 2,58</t>
+          <t>0,25; 2,63</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,54; 8,84</t>
+          <t>1,41; 8,81</t>
         </is>
       </c>
     </row>
@@ -1141,57 +1141,57 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,15; 2,66</t>
+          <t>0,16; 2,71</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,39; 3,1</t>
+          <t>0,39; 3,34</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,45; 5,75</t>
+          <t>1,32; 5,77</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,76; 3,85</t>
+          <t>0,79; 3,8</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,09; 8,16</t>
+          <t>2,26; 8,66</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,19; 4,62</t>
+          <t>0,2; 4,46</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,59; 5,82</t>
+          <t>1,47; 5,88</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,67; 3,34</t>
+          <t>0,77; 3,36</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,41; 5,99</t>
+          <t>1,53; 6,12</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,55; 3,42</t>
+          <t>0,53; 3,4</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,94; 5,12</t>
+          <t>1,99; 5,11</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,3; 4,53</t>
+          <t>1,31; 4,84</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,31; 3,17</t>
+          <t>1,35; 3,23</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,0; 3,39</t>
+          <t>0,9; 3,2</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,94; 4,64</t>
+          <t>1,91; 4,54</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,98; 5,16</t>
+          <t>1,98; 4,93</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,67; 4,2</t>
+          <t>1,69; 4,15</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,36; 3,75</t>
+          <t>1,35; 3,83</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2,84; 5,91</t>
+          <t>2,88; 5,83</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,91; 4,17</t>
+          <t>1,98; 4,18</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,63; 3,22</t>
+          <t>1,73; 3,24</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,29; 2,94</t>
+          <t>1,37; 2,92</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,77; 4,91</t>
+          <t>2,72; 4,82</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ09_A-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IQ09_A-Habitat-trans_orig.xlsx
@@ -731,47 +731,47 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,74; 10,24</t>
+          <t>1,78; 10,26</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,18; 5,17</t>
+          <t>0,33; 5,17</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,24; 7,79</t>
+          <t>1,31; 7,57</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,76; 4,75</t>
+          <t>0,75; 4,6</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,23; 6,85</t>
+          <t>1,27; 7,19</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,77; 3,73</t>
+          <t>0,74; 3,83</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,97; 5,81</t>
+          <t>1,75; 5,57</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,94; 3,83</t>
+          <t>0,87; 3,41</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,15; 7,25</t>
+          <t>2,26; 7,12</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,9; 3,29</t>
+          <t>1,0; 3,44</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,06; 4,15</t>
+          <t>1,0; 4,02</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,85; 5,84</t>
+          <t>0,94; 6,18</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,36; 2,81</t>
+          <t>0,4; 2,82</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,13; 8,23</t>
+          <t>2,51; 8,44</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,26; 4,7</t>
+          <t>1,16; 4,64</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,98; 7,83</t>
+          <t>2,12; 7,73</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,47; 6,82</t>
+          <t>2,51; 6,69</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,28; 6,53</t>
+          <t>2,14; 6,12</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,45; 3,62</t>
+          <t>1,37; 3,69</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,83; 5,52</t>
+          <t>1,83; 5,55</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,08; 4,83</t>
+          <t>2,01; 4,93</t>
         </is>
       </c>
     </row>
@@ -996,22 +996,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,8</t>
+          <t>0,0; 10,46</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,63; 5,61</t>
+          <t>0,56; 6,45</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,6</t>
+          <t>0,0; 1,57</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,42; 7,3</t>
+          <t>0,39; 7,84</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1021,37 +1021,37 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,89</t>
+          <t>0,0; 0,82</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,16; 3,44</t>
+          <t>0,16; 3,9</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,02; 12,15</t>
+          <t>0,87; 11,71</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,03; 8,11</t>
+          <t>1,0; 7,83</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,41; 2,94</t>
+          <t>0,38; 3,24</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,25; 2,63</t>
+          <t>0,24; 2,66</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,41; 8,81</t>
+          <t>1,52; 9,42</t>
         </is>
       </c>
     </row>
@@ -1141,57 +1141,57 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,16; 2,71</t>
+          <t>0,15; 2,83</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,39; 3,34</t>
+          <t>0,35; 3,19</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,32; 5,77</t>
+          <t>1,36; 5,84</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,79; 3,8</t>
+          <t>0,76; 3,96</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,26; 8,66</t>
+          <t>2,18; 8,08</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,2; 4,46</t>
+          <t>0,2; 4,34</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,47; 5,88</t>
+          <t>1,61; 5,73</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,77; 3,36</t>
+          <t>0,69; 3,6</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,53; 6,12</t>
+          <t>1,53; 6,1</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,53; 3,4</t>
+          <t>0,61; 3,34</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,99; 5,11</t>
+          <t>2,06; 5,2</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,31; 4,84</t>
+          <t>1,31; 4,51</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,35; 3,23</t>
+          <t>1,29; 3,15</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,9; 3,2</t>
+          <t>0,92; 3,22</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,91; 4,54</t>
+          <t>2,1; 4,72</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,98; 4,93</t>
+          <t>1,86; 4,79</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,69; 4,15</t>
+          <t>1,63; 4,11</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,35; 3,83</t>
+          <t>1,32; 3,8</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2,88; 5,83</t>
+          <t>2,75; 5,9</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,98; 4,18</t>
+          <t>1,97; 4,22</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,73; 3,24</t>
+          <t>1,66; 3,21</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,37; 2,92</t>
+          <t>1,32; 3,0</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,72; 4,82</t>
+          <t>2,79; 4,93</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ09_A-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IQ09_A-Habitat-trans_orig.xlsx
@@ -532,7 +532,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -540,7 +540,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -648,42 +648,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>2,25</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>3,84</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2,24</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>3,24</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>2,15</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>2,95</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>1,24</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>5,8</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>2,25</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>3,84</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>2,24</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>3,29</t>
+          <t>6,06</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>4,48</t>
+          <t>4,69</t>
         </is>
       </c>
     </row>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>0,34; 5,17</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>1,43; 7,67</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0,41; 4,72</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>1,12; 6,75</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>0,0; 4,0</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>1,2; 4,43</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0,97; 4,31</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>0,4; 2,0</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>1,78; 10,26</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>0,33; 5,17</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>1,31; 7,57</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>0,75; 4,6</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,27; 7,19</t>
+          <t>1,85; 10,68</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,74; 3,83</t>
+          <t>0,86; 3,89</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,75; 5,57</t>
+          <t>1,89; 5,56</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,87; 3,41</t>
+          <t>0,83; 3,35</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,26; 7,12</t>
+          <t>2,44; 7,98</t>
         </is>
       </c>
     </row>
@@ -788,42 +788,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>4,66</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>2,48</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>4,06</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>4,26</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>2,17</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>2,11</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>2,4</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>1,92</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>4,66</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>2,48</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>4,06</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>4,3</t>
+          <t>1,07</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>3,14</t>
+          <t>3,13</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,0; 3,44</t>
+          <t>2,27; 7,87</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,0; 4,02</t>
+          <t>1,19; 4,76</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,94; 6,18</t>
+          <t>1,99; 7,54</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,4; 2,82</t>
+          <t>2,47; 6,86</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,51; 8,44</t>
+          <t>0,99; 3,43</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,16; 4,64</t>
+          <t>0,99; 4,22</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,12; 7,73</t>
+          <t>0,84; 5,88</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,51; 6,69</t>
+          <t>0,35; 2,15</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,14; 6,12</t>
+          <t>2,18; 6,26</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,37; 3,69</t>
+          <t>1,31; 3,6</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,83; 5,55</t>
+          <t>1,69; 5,44</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,01; 4,93</t>
+          <t>1,84; 5,01</t>
         </is>
       </c>
     </row>
@@ -928,42 +928,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>2,19</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0,3</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>1,21</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>5,25</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>4,85</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>1,94</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>0,4</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>2,87</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>2,19</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>0,3</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>1,21</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>4,94</t>
+          <t>3,09</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>4,12</t>
+          <t>4,39</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>0,0; 6,26</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 0,94</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>0,16; 3,91</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>0,96; 12,49</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
           <t>0,0; 10,46</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>0,56; 6,45</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 1,57</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>0,39; 7,84</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 6,26</t>
-        </is>
-      </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,82</t>
+          <t>0,55; 6,03</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,16; 3,9</t>
+          <t>0,0; 1,59</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,87; 11,71</t>
+          <t>0,35; 7,46</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,0; 7,83</t>
+          <t>1,05; 8,16</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,38; 3,24</t>
+          <t>0,4; 3,09</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,24; 2,66</t>
+          <t>0,24; 2,58</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,52; 9,42</t>
+          <t>1,58; 9,32</t>
         </is>
       </c>
     </row>
@@ -1068,42 +1068,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>1,99</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>4,8</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1,34</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>3,64</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>0,8</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>0,93</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>1,51</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>3,67</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>1,99</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>4,8</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>1,34</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>3,54</t>
+          <t>3,79</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>3,59</t>
+          <t>3,7</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>0,76; 3,85</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>2,09; 8,16</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0,19; 4,62</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>1,59; 5,99</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>0,0; 2,0</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>0,15; 2,83</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>0,35; 3,19</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>1,36; 5,84</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>0,76; 3,96</t>
-        </is>
-      </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,18; 8,08</t>
+          <t>0,15; 2,66</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,2; 4,34</t>
+          <t>0,39; 3,1</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,61; 5,73</t>
+          <t>1,49; 5,82</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,69; 3,6</t>
+          <t>0,67; 3,34</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,53; 6,1</t>
+          <t>1,41; 5,99</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,61; 3,34</t>
+          <t>0,55; 3,42</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,06; 5,2</t>
+          <t>1,97; 5,25</t>
         </is>
       </c>
     </row>
@@ -1208,42 +1208,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>3,12</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>2,67</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>2,29</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>4,18</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>2,56</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>2,02</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>1,66</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>3,1</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>3,12</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>2,67</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>2,29</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>4,1</t>
+          <t>3,32</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>3,66</t>
+          <t>3,83</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,31; 4,51</t>
+          <t>1,98; 5,16</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,29; 3,15</t>
+          <t>1,67; 4,2</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,92; 3,22</t>
+          <t>1,36; 3,75</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,1; 4,72</t>
+          <t>2,85; 6,14</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,86; 4,79</t>
+          <t>1,3; 4,53</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,63; 4,11</t>
+          <t>1,31; 3,17</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,32; 3,8</t>
+          <t>1,0; 3,39</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2,75; 5,9</t>
+          <t>1,88; 5,19</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,97; 4,22</t>
+          <t>1,91; 4,17</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,66; 3,21</t>
+          <t>1,63; 3,22</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,32; 3,0</t>
+          <t>1,29; 2,94</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,79; 4,93</t>
+          <t>2,84; 5,34</t>
         </is>
       </c>
     </row>
